--- a/naver-place-crawler/results_health/종로_PT.xlsx
+++ b/naver-place-crawler/results_health/종로_PT.xlsx
@@ -423,7 +423,7 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="46" customWidth="1" min="7" max="7"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>아크로짐 안국역점 헬스&amp;PT</t>
+          <t>백퍼센트짐 헬스&amp;골프</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>acrogym7487@naver.com</t>
+          <t>100percentgym2@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1448-0665</t>
+          <t>0507-1345-3897</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 삼일대로 469 서원빌딩 지하2층 아크로짐 안국역점 헬스앤PT</t>
+          <t>서울특별시 종로구 대학로 146 B101호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/acrogym13</t>
+          <t>https://www.instagram.com/100percent_gym_no.2/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>601</v>
+        <v>1282</v>
       </c>
       <c r="Q2" t="n">
-        <v>264</v>
+        <v>579</v>
       </c>
       <c r="R2" t="n">
-        <v>865</v>
+        <v>1861</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>17919627</t>
+          <t>1501906296</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/17919627</t>
+          <t>https://m.place.naver.com/place/1501906296</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -711,13 +711,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="Q3" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="R3" t="n">
-        <v>1034</v>
+        <v>1037</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -808,10 +808,10 @@
         <v>193</v>
       </c>
       <c r="Q4" t="n">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="R4" t="n">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -842,44 +842,44 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>턴온피트니스 PT 광화문점</t>
+          <t>스포짐 종로점 PT&amp;헬스</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>tndnjsqkek@naver.com</t>
+          <t>spogym14@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1380-6792</t>
+          <t>0507-1309-7981</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로5길 13 2층</t>
+          <t>서울특별시 종로구 청계천로 35 관정빌딩 B2 스포짐 종로점</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/strength_kon</t>
+          <t>https://booking.naver.com/booking/6/bizes/396022</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -899,13 +899,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>33</v>
+        <v>235</v>
       </c>
       <c r="Q5" t="n">
-        <v>242</v>
+        <v>694</v>
       </c>
       <c r="R5" t="n">
-        <v>275</v>
+        <v>929</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -914,12 +914,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2018780751</t>
+          <t>1240026286</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2018780751</t>
+          <t>https://m.place.naver.com/place/1240026286</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -936,44 +936,44 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>스포짐 종로점 PT&amp;헬스</t>
+          <t>턴온피트니스 PT 광화문점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>spogym14@naver.com</t>
+          <t>tndnjsqkek@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1309-7981</t>
+          <t>0507-1380-6792</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 청계천로 35 관정빌딩 B2 스포짐 종로점</t>
+          <t>서울특별시 종로구 종로5길 13 2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/6/bizes/396022</t>
+          <t>https://www.instagram.com/strength_kon</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>235</v>
+        <v>33</v>
       </c>
       <c r="Q6" t="n">
-        <v>694</v>
+        <v>236</v>
       </c>
       <c r="R6" t="n">
-        <v>929</v>
+        <v>269</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1240026286</t>
+          <t>2018780751</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1240026286</t>
+          <t>https://m.place.naver.com/place/2018780751</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1090,10 +1090,10 @@
         <v>155</v>
       </c>
       <c r="Q7" t="n">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="R7" t="n">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1213,34 +1213,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>마이크로스튜디오 시청점</t>
+          <t>베럴짐 광화문점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>cityhallmicro@naver.com</t>
+          <t>bettergym1@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1346-2162</t>
+          <t>0507-1353-9536</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 중구 다동길 43 한외빌딩 지하1층 마이크로스튜디오</t>
+          <t>서울특별시 종로구 새문안로3길 30 대우빌딩 지하1층 123호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://microstudio.kr</t>
+          <t>https://blog.naver.com/bettergym1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>239</v>
+        <v>830</v>
       </c>
       <c r="Q9" t="n">
-        <v>734</v>
+        <v>1829</v>
       </c>
       <c r="R9" t="n">
-        <v>973</v>
+        <v>2659</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1290,12 +1290,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1381838006</t>
+          <t>1663517273</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1381838006</t>
+          <t>https://m.place.naver.com/place/1663517273</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1312,33 +1312,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>버핏그라운드 광화문</t>
+          <t>아크로짐 안국역점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>partner@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>acrogym7487@naver.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1314-3624</t>
+          <t>0507-1448-0665</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 중구 세종대로 136 B1, B2층</t>
+          <t>서울특별시 종로구 삼일대로 469 서원빌딩 지하2층 아크로짐 안국역점 헬스앤PT</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://pt.butfitground.com/</t>
+          <t>https://www.instagram.com/acrogym13</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1353,7 +1349,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1364,7 +1360,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1373,13 +1369,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>291</v>
+        <v>601</v>
       </c>
       <c r="Q10" t="n">
-        <v>338</v>
+        <v>265</v>
       </c>
       <c r="R10" t="n">
-        <v>629</v>
+        <v>866</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,12 +1384,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1720388209</t>
+          <t>17919627</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1720388209</t>
+          <t>https://m.place.naver.com/place/17919627</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1410,29 +1406,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>휘트니스피플 우먼 동묘앞역점</t>
+          <t>헬스보이짐앤필라걸 서울시청점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>fpeoplew1@naver.com</t>
+          <t>healthboy52@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1394-3912</t>
+          <t>0507-1345-4222</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 335 7층</t>
+          <t>서울특별시 중구 무교로 21 지하1층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.fitnesspeople.co.kr/</t>
+          <t>https://www.instagram.com/healthboy52/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1467,13 +1463,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>156</v>
+        <v>990</v>
       </c>
       <c r="Q11" t="n">
-        <v>34</v>
+        <v>1237</v>
       </c>
       <c r="R11" t="n">
-        <v>190</v>
+        <v>2227</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,12 +1478,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2051051265</t>
+          <t>1954406967</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2051051265</t>
+          <t>https://m.place.naver.com/place/1954406967</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/종로_PT.xlsx
+++ b/naver-place-crawler/results_health/종로_PT.xlsx
@@ -421,9 +421,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="46" customWidth="1" min="7" max="7"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>백퍼센트짐 헬스&amp;골프</t>
+          <t>아크로짐 안국역점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>100percentgym2@naver.com</t>
+          <t>acrogym7487@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1345-3897</t>
+          <t>0507-1448-0665</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 대학로 146 B101호</t>
+          <t>서울특별시 종로구 삼일대로 469 서원빌딩 지하2층 아크로짐 안국역점 헬스앤PT</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/100percent_gym_no.2/</t>
+          <t>https://www.instagram.com/acrogym13</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1282</v>
+        <v>617</v>
       </c>
       <c r="Q2" t="n">
-        <v>579</v>
+        <v>274</v>
       </c>
       <c r="R2" t="n">
-        <v>1861</v>
+        <v>891</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1501906296</t>
+          <t>17919627</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1501906296</t>
+          <t>https://m.place.naver.com/place/17919627</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -658,25 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>어메이징휘트니스 헬스&amp;PT 종로점</t>
+          <t>백퍼센트짐 헬스&amp;골프</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>amazinggym_jr@naver.com</t>
+          <t>100percentgym2@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0507-1345-3897</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 수표로 96 10층</t>
+          <t>서울특별시 종로구 대학로 146 B101호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/amazinggym_jr</t>
+          <t>https://www.instagram.com/100percent_gym_no.2/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -691,7 +695,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -711,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>773</v>
+        <v>1296</v>
       </c>
       <c r="Q3" t="n">
-        <v>264</v>
+        <v>606</v>
       </c>
       <c r="R3" t="n">
-        <v>1037</v>
+        <v>1902</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -726,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1713671108</t>
+          <t>1501906296</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1713671108</t>
+          <t>https://m.place.naver.com/place/1501906296</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -805,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q4" t="n">
-        <v>869</v>
+        <v>883</v>
       </c>
       <c r="R4" t="n">
-        <v>1062</v>
+        <v>1078</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -830,7 +834,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -874,7 +878,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -902,10 +906,10 @@
         <v>235</v>
       </c>
       <c r="Q5" t="n">
-        <v>694</v>
+        <v>703</v>
       </c>
       <c r="R5" t="n">
-        <v>929</v>
+        <v>938</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -924,7 +928,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -993,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q6" t="n">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="R6" t="n">
-        <v>269</v>
+        <v>230</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1018,7 +1022,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1030,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>관철동헬스클럽 PT</t>
+          <t>샤머니짐 헬스&amp;PT 동대문점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>gwancheol_dong@naver.com</t>
+          <t>resort_14@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>02-730-0908</t>
+          <t>0507-1424-7205</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 삼일대로15길 6 2층</t>
+          <t>서울특별시 중구 을지로 264 6층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gwancheol_dong</t>
+          <t>https://blog.naver.com/resort_14</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1087,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>155</v>
+        <v>526</v>
       </c>
       <c r="Q7" t="n">
-        <v>417</v>
+        <v>497</v>
       </c>
       <c r="R7" t="n">
-        <v>572</v>
+        <v>1023</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1102,56 +1106,56 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1564637519</t>
+          <t>1075549287</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1564637519</t>
+          <t>https://m.place.naver.com/place/1075549287</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>좋은습관 PT STUDIO 광화문</t>
+          <t>헬스보이짐앤필라걸 서울시청점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>bru_425@naver.com</t>
+          <t>healthboy52@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1387-2087</t>
+          <t>0507-1345-4222</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 삼봉로 57 지하1층</t>
+          <t>서울특별시 중구 무교로 21 지하1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://vo.la/MYoFyX</t>
+          <t>https://www.instagram.com/healthboy52/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1181,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>530</v>
+        <v>1006</v>
       </c>
       <c r="Q8" t="n">
-        <v>79</v>
+        <v>1256</v>
       </c>
       <c r="R8" t="n">
-        <v>609</v>
+        <v>2262</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1196,56 +1200,60 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1769012256</t>
+          <t>1954406967</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1769012256</t>
+          <t>https://m.place.naver.com/place/1954406967</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>베럴짐 광화문점</t>
+          <t>마이크로스튜디오 시청점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bettergym1@naver.com</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>cityhallmicro@naver.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>owner@microstudio.kr</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1353-9536</t>
+          <t>0507-1346-2162</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 새문안로3길 30 대우빌딩 지하1층 123호</t>
+          <t>서울특별시 중구 다동길 43 한외빌딩 지하1층 마이크로스튜디오</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bettergym1</t>
+          <t>https://microstudio.kr</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1266,7 +1274,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1275,13 +1283,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>830</v>
+        <v>239</v>
       </c>
       <c r="Q9" t="n">
-        <v>1829</v>
+        <v>744</v>
       </c>
       <c r="R9" t="n">
-        <v>2659</v>
+        <v>983</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1290,17 +1298,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1663517273</t>
+          <t>1381838006</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1663517273</t>
+          <t>https://m.place.naver.com/place/1381838006</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1312,29 +1320,33 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>아크로짐 안국역점 헬스&amp;PT</t>
+          <t>버핏그라운드 광화문</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>acrogym7487@naver.com</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>butfitseoul@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1448-0665</t>
+          <t>0507-1314-3624</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 삼일대로 469 서원빌딩 지하2층 아크로짐 안국역점 헬스앤PT</t>
+          <t>서울특별시 중구 세종대로 136 B1, B2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/acrogym13</t>
+          <t>https://pt.butfitground.com/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1349,7 +1361,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1360,7 +1372,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1369,13 +1381,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>601</v>
+        <v>291</v>
       </c>
       <c r="Q10" t="n">
-        <v>265</v>
+        <v>369</v>
       </c>
       <c r="R10" t="n">
-        <v>866</v>
+        <v>660</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1384,17 +1396,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>17919627</t>
+          <t>1720388209</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/17919627</t>
+          <t>https://m.place.naver.com/place/1720388209</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1406,34 +1418,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>헬스보이짐앤필라걸 서울시청점</t>
+          <t>휘트니스피플 우먼 동묘앞역점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>healthboy52@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>fpeoplew1@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>psi@fitnesspeople.co.kr</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1345-4222</t>
+          <t>0507-1394-3912</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 중구 무교로 21 지하1층</t>
+          <t>서울특별시 종로구 종로 335 7층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/healthboy52/</t>
+          <t>https://www.fitnesspeople.co.kr/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1443,7 +1459,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1463,13 +1479,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>990</v>
+        <v>166</v>
       </c>
       <c r="Q11" t="n">
-        <v>1237</v>
+        <v>38</v>
       </c>
       <c r="R11" t="n">
-        <v>2227</v>
+        <v>204</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1478,17 +1494,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1954406967</t>
+          <t>2051051265</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1954406967</t>
+          <t>https://m.place.naver.com/place/2051051265</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/종로_PT.xlsx
+++ b/naver-place-crawler/results_health/종로_PT.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="29" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -646,41 +646,41 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>백퍼센트짐 헬스&amp;골프</t>
+          <t>스포짐 종각점 PT&amp;헬스</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>100percentgym2@naver.com</t>
+          <t>spogym12@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1345-3897</t>
+          <t>0507-1351-0020</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 대학로 146 B101호</t>
+          <t>서울특별시 종로구 삼봉로 95 대성스카이렉스 B1 스포짐 종각점</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/100percent_gym_no.2/</t>
+          <t>https://blog.naver.com/spogym12</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1296</v>
+        <v>195</v>
       </c>
       <c r="Q3" t="n">
-        <v>606</v>
+        <v>883</v>
       </c>
       <c r="R3" t="n">
-        <v>1902</v>
+        <v>1078</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1501906296</t>
+          <t>1991410927</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1501906296</t>
+          <t>https://m.place.naver.com/place/1991410927</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -752,39 +752,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>스포짐 종각점 PT&amp;헬스</t>
+          <t>스포짐 종로점 PT&amp;헬스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>spogym12@naver.com</t>
+          <t>spogym14@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1351-0020</t>
+          <t>0507-1309-7981</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 삼봉로 95 대성스카이렉스 B1 스포짐 종각점</t>
+          <t>서울특별시 종로구 청계천로 35 관정빌딩 B2 스포짐 종로점</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spogym12</t>
+          <t>https://booking.naver.com/booking/6/bizes/396022</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>195</v>
+        <v>235</v>
       </c>
       <c r="Q4" t="n">
-        <v>883</v>
+        <v>705</v>
       </c>
       <c r="R4" t="n">
-        <v>1078</v>
+        <v>940</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1991410927</t>
+          <t>1240026286</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1991410927</t>
+          <t>https://m.place.naver.com/place/1240026286</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -846,34 +846,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>스포짐 종로점 PT&amp;헬스</t>
+          <t>턴온피트니스 PT 광화문점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>spogym14@naver.com</t>
+          <t>tndnjsqkek@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1309-7981</t>
+          <t>0507-1380-6792</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 청계천로 35 관정빌딩 B2 스포짐 종로점</t>
+          <t>서울특별시 종로구 종로5길 13 2층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/6/bizes/396022</t>
+          <t>https://www.instagram.com/strength_kon</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>235</v>
+        <v>34</v>
       </c>
       <c r="Q5" t="n">
-        <v>703</v>
+        <v>206</v>
       </c>
       <c r="R5" t="n">
-        <v>938</v>
+        <v>240</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1240026286</t>
+          <t>2018780751</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1240026286</t>
+          <t>https://m.place.naver.com/place/2018780751</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -940,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>턴온피트니스 PT 광화문점</t>
+          <t>샤머니짐 헬스&amp;PT 동대문점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>tndnjsqkek@naver.com</t>
+          <t>resort_14@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1380-6792</t>
+          <t>0507-1424-7205</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로5길 13 2층</t>
+          <t>서울특별시 중구 을지로 264 6층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/strength_kon</t>
+          <t>https://blog.naver.com/resort_14</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>34</v>
+        <v>526</v>
       </c>
       <c r="Q6" t="n">
-        <v>196</v>
+        <v>498</v>
       </c>
       <c r="R6" t="n">
-        <v>230</v>
+        <v>1024</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,51 +1012,51 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2018780751</t>
+          <t>1075549287</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2018780751</t>
+          <t>https://m.place.naver.com/place/1075549287</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>샤머니짐 헬스&amp;PT 동대문점</t>
+          <t>스포애니 종각역점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>resort_14@naver.com</t>
+          <t>spoany113@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1424-7205</t>
+          <t>0507-1443-9618</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 264 6층</t>
+          <t>서울특별시 종로구 종로 68 B1, B2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/resort_14</t>
+          <t>https://blog.naver.com/spoany113/223842396671</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>526</v>
+        <v>993</v>
       </c>
       <c r="Q7" t="n">
-        <v>497</v>
+        <v>1656</v>
       </c>
       <c r="R7" t="n">
-        <v>1023</v>
+        <v>2649</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,56 +1106,60 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1075549287</t>
+          <t>1732112209</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1075549287</t>
+          <t>https://m.place.naver.com/place/1732112209</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>헬스보이짐앤필라걸 서울시청점</t>
+          <t>마이크로스튜디오 시청점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>healthboy52@naver.com</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>cityhallmicro@naver.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>owner@microstudio.kr</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1345-4222</t>
+          <t>0507-1346-2162</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 중구 무교로 21 지하1층</t>
+          <t>서울특별시 중구 다동길 43 한외빌딩 지하1층 마이크로스튜디오</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/healthboy52/</t>
+          <t>https://microstudio.kr</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1165,7 +1169,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1176,7 +1180,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1185,13 +1189,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1006</v>
+        <v>239</v>
       </c>
       <c r="Q8" t="n">
-        <v>1256</v>
+        <v>744</v>
       </c>
       <c r="R8" t="n">
-        <v>2262</v>
+        <v>983</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,55 +1204,47 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1954406967</t>
+          <t>1381838006</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1954406967</t>
+          <t>https://m.place.naver.com/place/1381838006</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>마이크로스튜디오 시청점</t>
+          <t>팀버핏 광화문</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>cityhallmicro@naver.com</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>owner@microstudio.kr</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0507-1346-2162</t>
-        </is>
-      </c>
+          <t>jhjh5508@naver.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 중구 다동길 43 한외빌딩 지하1층 마이크로스튜디오</t>
+          <t>서울특별시 중구 세종대로 136 지하 1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://microstudio.kr</t>
+          <t>https://www.teambutfit.com</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1263,7 +1259,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1274,7 +1270,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1283,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q9" t="n">
-        <v>744</v>
+        <v>34</v>
       </c>
       <c r="R9" t="n">
-        <v>983</v>
+        <v>274</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,29 +1294,29 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1381838006</t>
+          <t>1117727301</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1381838006</t>
+          <t>https://m.place.naver.com/place/1117727301</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>버핏그라운드 광화문</t>
+          <t>버핏그라운드 PT 광화문</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1335,23 +1331,23 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1314-3624</t>
+          <t>0507-1413-0755</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 중구 세종대로 136 B1, B2층</t>
+          <t>서울특별시 중구 세종대로 136 서울파이낸스센터 SFC B1, B2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://pt.butfitground.com/</t>
+          <t>https://www.butfitground.com/4steppt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1381,13 +1377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>291</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>369</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>660</v>
+        <v>1</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1396,17 +1392,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1720388209</t>
+          <t>2093030344</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1720388209</t>
+          <t>https://m.place.naver.com/place/2093030344</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1418,38 +1414,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>휘트니스피플 우먼 동묘앞역점</t>
+          <t>버핏그라운드 광화문</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>fpeoplew1@naver.com</t>
+          <t>butfitground@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>psi@fitnesspeople.co.kr</t>
+          <t>butfitseoul@butfitseoul.com</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1394-3912</t>
+          <t>0507-1314-3624</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 335 7층</t>
+          <t>서울특별시 중구 세종대로 136 B1, B2층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.fitnesspeople.co.kr/</t>
+          <t>https://pt.butfitground.com/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1470,7 +1466,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1479,13 +1475,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>166</v>
+        <v>292</v>
       </c>
       <c r="Q11" t="n">
-        <v>38</v>
+        <v>380</v>
       </c>
       <c r="R11" t="n">
-        <v>204</v>
+        <v>672</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1494,17 +1490,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2051051265</t>
+          <t>1720388209</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2051051265</t>
+          <t>https://m.place.naver.com/place/1720388209</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/종로_PT.xlsx
+++ b/naver-place-crawler/results_health/종로_PT.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="29" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="37" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>아크로짐 안국역점 헬스&amp;PT</t>
+          <t>백퍼센트짐 헬스&amp;골프</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>acrogym7487@naver.com</t>
+          <t>100percentgym2@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1448-0665</t>
+          <t>0507-1345-3897</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 삼일대로 469 서원빌딩 지하2층 아크로짐 안국역점 헬스앤PT</t>
+          <t>서울 종로구 대학로 146 B101호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/acrogym13</t>
+          <t>https://www.instagram.com/100percent_gym_no.2/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4d9zn</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>617</v>
+        <v>1298</v>
       </c>
       <c r="Q2" t="n">
-        <v>274</v>
+        <v>611</v>
       </c>
       <c r="R2" t="n">
-        <v>891</v>
+        <v>1909</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>17919627</t>
+          <t>1501906296</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/17919627</t>
+          <t>https://m.place.naver.com/place/1501906296</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -675,7 +679,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 삼봉로 95 대성스카이렉스 B1 스포짐 종각점</t>
+          <t>서울 종로구 삼봉로 95 대성스카이렉스 B1 스포짐 종각점</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wchlsb</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -769,7 +777,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 청계천로 35 관정빌딩 B2 스포짐 종로점</t>
+          <t>서울 종로구 청계천로 35 관정빌딩 B2 스포짐 종로점</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -794,10 +802,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4ulg5</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -863,7 +875,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로5길 13 2층</t>
+          <t>서울 종로구 종로5길 13 2층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -888,10 +900,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/witvn8b</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -906,10 +922,10 @@
         <v>34</v>
       </c>
       <c r="Q5" t="n">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="R5" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -957,7 +973,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 264 6층</t>
+          <t>서울 중구 을지로 264 6층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -982,10 +998,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5vnh2</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1051,7 +1071,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 68 B1, B2층</t>
+          <t>서울 종로구 종로 68 B1, B2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1076,10 +1096,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w6eii90</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1094,10 +1118,10 @@
         <v>993</v>
       </c>
       <c r="Q7" t="n">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="R7" t="n">
-        <v>2649</v>
+        <v>2648</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1128,33 +1152,33 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>마이크로스튜디오 시청점</t>
+          <t>버핏그라운드 PT 광화문</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cityhallmicro@naver.com</t>
+          <t>butfitground@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>owner@microstudio.kr</t>
+          <t>butfitseoul@butfitseoul.com</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1346-2162</t>
+          <t>0507-1413-0755</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 중구 다동길 43 한외빌딩 지하1층 마이크로스튜디오</t>
+          <t>서울 중구 세종대로 136 서울파이낸스센터 SFC B1, B2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://microstudio.kr</t>
+          <t>https://www.butfitground.com/4steppt</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1189,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>239</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>744</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>983</v>
+        <v>1</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1381838006</t>
+          <t>2093030344</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1381838006</t>
+          <t>https://m.place.naver.com/place/2093030344</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1221,30 +1245,38 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>팀버핏 광화문</t>
+          <t>마이크로스튜디오 시청점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>jhjh5508@naver.com</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+          <t>cityhallmicro@naver.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>owner@microstudio.kr</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1346-2162</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 중구 세종대로 136 지하 1층</t>
+          <t>서울 중구 다동길 43 한외빌딩 지하1층 마이크로스튜디오</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.teambutfit.com</t>
+          <t>https://microstudio.kr</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1259,18 +1291,22 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4rdsf</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1279,13 +1315,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q9" t="n">
-        <v>34</v>
+        <v>744</v>
       </c>
       <c r="R9" t="n">
-        <v>274</v>
+        <v>983</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,12 +1330,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1117727301</t>
+          <t>1381838006</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1117727301</t>
+          <t>https://m.place.naver.com/place/1381838006</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1311,43 +1347,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>버핏그라운드 PT 광화문</t>
+          <t>헬스보이짐앤필라걸 서울시청점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>butfitseoul@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>healthboy52@naver.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1413-0755</t>
+          <t>0507-1345-4222</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 중구 세종대로 136 서울파이낸스센터 SFC B1, B2층</t>
+          <t>서울 중구 무교로 21 지하1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.butfitground.com/4steppt</t>
+          <t>https://www.instagram.com/healthboy52/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1357,18 +1389,22 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4ag5u</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1377,13 +1413,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1012</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>1259</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>2271</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,12 +1428,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2093030344</t>
+          <t>1954406967</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2093030344</t>
+          <t>https://m.place.naver.com/place/1954406967</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1435,7 +1471,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 중구 세종대로 136 B1, B2층</t>
+          <t>서울 중구 세종대로 136 B1, B2층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1460,10 +1496,14 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w6v6jkj</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>O</t>
@@ -1478,10 +1518,10 @@
         <v>292</v>
       </c>
       <c r="Q11" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="R11" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1499,6 +1539,108 @@
         </is>
       </c>
       <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>휘트니스피플 우먼 동묘앞역점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>fpeoplew1@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>psi@fitnesspeople.co.kr</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1394-3912</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>서울 종로구 종로 335 7층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.fitnesspeople.co.kr/</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w3icahd</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>167</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>38</v>
+      </c>
+      <c r="R12" t="n">
+        <v>205</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2051051265</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2051051265</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/종로_PT.xlsx
+++ b/naver-place-crawler/results_health/종로_PT.xlsx
@@ -426,13 +426,13 @@
     <col width="25" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>자마이카피트니스앤스파 종로점</t>
+          <t>아크로짐 안국역점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>jamaica-jongno@naver.com</t>
+          <t>acrogym7487@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1317-8533</t>
+          <t>0507-1448-0665</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 19 르메이에르종로타운1 지하2층~지하3층</t>
+          <t>서울특별시 종로구 삼일대로 469 서원빌딩 지하2층 아크로짐 안국역점 헬스앤PT</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/acrogym13</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w40ti0</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3057</v>
+        <v>616</v>
       </c>
       <c r="Q2" t="n">
-        <v>503</v>
+        <v>275</v>
       </c>
       <c r="R2" t="n">
-        <v>3560</v>
+        <v>891</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,51 +636,51 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1716544631</t>
+          <t>17919627</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1716544631</t>
+          <t>https://m.place.naver.com/place/17919627</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>스포짐 종각점 PT&amp;헬스</t>
+          <t>자마이카피트니스앤스파 종로점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>spogym12@naver.com</t>
+          <t>jamaica-jongno@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1351-0020</t>
+          <t>0507-1317-8533</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 삼봉로 95 대성스카이렉스 B1 스포짐 종각점</t>
+          <t>서울특별시 종로구 종로 19 르메이에르종로타운1 지하2층~지하3층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/jamaica-jongno</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,24 +690,20 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wchlsb</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -723,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>195</v>
+        <v>3057</v>
       </c>
       <c r="Q3" t="n">
-        <v>883</v>
+        <v>503</v>
       </c>
       <c r="R3" t="n">
-        <v>1078</v>
+        <v>3560</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1991410927</t>
+          <t>1716544631</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1991410927</t>
+          <t>https://m.place.naver.com/place/1716544631</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -760,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>스포짐 종로점 PT&amp;헬스</t>
+          <t>스포짐 종각점 PT&amp;헬스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>spogym14@naver.com</t>
+          <t>spogym12@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1309-7981</t>
+          <t>0507-1351-0020</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 청계천로 35 관정빌딩 B2 스포짐 종로점</t>
+          <t>서울특별시 종로구 삼봉로 95 대성스카이렉스 B1 스포짐 종각점</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/spogym12</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -792,24 +784,20 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4ulg5</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -821,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>235</v>
+        <v>195</v>
       </c>
       <c r="Q4" t="n">
-        <v>709</v>
+        <v>883</v>
       </c>
       <c r="R4" t="n">
-        <v>944</v>
+        <v>1078</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1240026286</t>
+          <t>1991410927</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1240026286</t>
+          <t>https://m.place.naver.com/place/1991410927</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -858,34 +846,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>턴온피트니스 PT 광화문점</t>
+          <t>스포짐 종로점 PT&amp;헬스</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>tndnjsqkek@naver.com</t>
+          <t>spogym14@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1380-6792</t>
+          <t>0507-1309-7981</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로5길 13 2층</t>
+          <t>서울특별시 종로구 청계천로 35 관정빌딩 B2 스포짐 종로점</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://booking.naver.com/booking/6/bizes/396022</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -895,19 +883,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/witvn8b</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -919,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>34</v>
+        <v>235</v>
       </c>
       <c r="Q5" t="n">
-        <v>211</v>
+        <v>712</v>
       </c>
       <c r="R5" t="n">
-        <v>245</v>
+        <v>947</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,51 +918,51 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2018780751</t>
+          <t>1240026286</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2018780751</t>
+          <t>https://m.place.naver.com/place/1240026286</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>스포애니 종각역점</t>
+          <t>턴온피트니스 PT 광화문점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>spoany113@naver.com</t>
+          <t>tndnjsqkek@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1443-9618</t>
+          <t>0507-1380-6792</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 68 B1, B2층</t>
+          <t>서울특별시 종로구 종로5길 13 2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/strength_kon</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -988,7 +972,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -998,14 +982,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w6eii90</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1017,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>995</v>
+        <v>34</v>
       </c>
       <c r="Q6" t="n">
-        <v>1660</v>
+        <v>212</v>
       </c>
       <c r="R6" t="n">
-        <v>2655</v>
+        <v>246</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,51 +1012,51 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1732112209</t>
+          <t>2018780751</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1732112209</t>
+          <t>https://m.place.naver.com/place/2018780751</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>샤머니짐 헬스&amp;PT 동대문점</t>
+          <t>스포애니 종각역점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>resort_14@naver.com</t>
+          <t>spoany113@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1424-7205</t>
+          <t>0507-1443-9618</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 264 6층</t>
+          <t>서울특별시 종로구 종로 68 B1, B2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/spoany113/223842396671</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1086,24 +1066,20 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5vnh2</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1115,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>527</v>
+        <v>995</v>
       </c>
       <c r="Q7" t="n">
-        <v>498</v>
+        <v>1660</v>
       </c>
       <c r="R7" t="n">
-        <v>1025</v>
+        <v>2655</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,17 +1106,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1075549287</t>
+          <t>1732112209</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1075549287</t>
+          <t>https://m.place.naver.com/place/1732112209</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1152,38 +1128,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>마이크로스튜디오 시청점</t>
+          <t>샤머니짐 헬스&amp;PT 동대문점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cityhallmicro@naver.com</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>owner@microstudio.kr</t>
-        </is>
-      </c>
+          <t>resort_14@naver.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1346-2162</t>
+          <t>0507-1424-7205</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 중구 다동길 43 한외빌딩 지하1층 마이크로스튜디오</t>
+          <t>서울특별시 중구 을지로 264 6층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://microstudio.kr</t>
+          <t>https://blog.naver.com/resort_14</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1198,17 +1170,13 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4rdsf</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1217,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>239</v>
+        <v>527</v>
       </c>
       <c r="Q8" t="n">
-        <v>744</v>
+        <v>498</v>
       </c>
       <c r="R8" t="n">
-        <v>983</v>
+        <v>1025</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1232,17 +1200,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1381838006</t>
+          <t>1075549287</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1381838006</t>
+          <t>https://m.place.naver.com/place/1075549287</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1254,33 +1222,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>버핏그라운드 광화문</t>
+          <t>베럴짐 광화문점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>partner@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>bettergym1@naver.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1314-3624</t>
+          <t>0507-1353-9536</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 중구 세종대로 136 B1, B2층</t>
+          <t>서울특별시 종로구 새문안로3길 30 대우빌딩 지하1층 123호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://pt.butfitground.com/</t>
+          <t>https://blog.naver.com/bettergym1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1300,17 +1264,13 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w6v6jkj</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1319,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>292</v>
+        <v>834</v>
       </c>
       <c r="Q9" t="n">
-        <v>388</v>
+        <v>1817</v>
       </c>
       <c r="R9" t="n">
-        <v>680</v>
+        <v>2651</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1334,55 +1294,55 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1720388209</t>
+          <t>1663517273</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1720388209</t>
+          <t>https://m.place.naver.com/place/1663517273</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>휘트니스피플 우먼 동묘앞역점</t>
+          <t>마이크로스튜디오 시청점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>fpeoplew1@naver.com</t>
+          <t>cityhallmicro@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>psi@fitnesspeople.co.kr</t>
+          <t>owner@microstudio.kr</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1394-3912</t>
+          <t>0507-1346-2162</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 335 7층</t>
+          <t>서울특별시 중구 다동길 43 한외빌딩 지하1층 마이크로스튜디오</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.fitnesspeople.co.kr/</t>
+          <t>https://microstudio.kr</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1402,17 +1362,13 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w3icahd</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1421,13 +1377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>167</v>
+        <v>239</v>
       </c>
       <c r="Q10" t="n">
-        <v>38</v>
+        <v>744</v>
       </c>
       <c r="R10" t="n">
-        <v>205</v>
+        <v>983</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1436,51 +1392,55 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2051051265</t>
+          <t>1381838006</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2051051265</t>
+          <t>https://m.place.naver.com/place/1381838006</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>인피티 INPT</t>
+          <t>버핏그라운드 광화문</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>inhoon1205@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>partner@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1452-1183</t>
+          <t>0507-1314-3624</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 새문안로3길 36 . 지하1층 118호</t>
+          <t>서울특별시 중구 세종대로 136 B1, B2층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://pt.butfitground.com/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1490,27 +1450,23 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wwez5ga</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1519,13 +1475,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>90</v>
+        <v>292</v>
       </c>
       <c r="Q11" t="n">
-        <v>52</v>
+        <v>388</v>
       </c>
       <c r="R11" t="n">
-        <v>142</v>
+        <v>680</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1534,17 +1490,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2020129659</t>
+          <t>1720388209</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2020129659</t>
+          <t>https://m.place.naver.com/place/1720388209</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1556,56 +1512,56 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>스포애니 서울시청역점</t>
+          <t>휘트니스피플 우먼 동묘앞역점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>spoany_73@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>fpeoplew1@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>psi@fitnesspeople.co.kr</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1335-5273</t>
+          <t>0507-1394-3912</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>서울특별시 중구 서소문로 124 씨티스퀘어 B2층</t>
+          <t>서울특별시 종로구 종로 335 7층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.fitnesspeople.co.kr/</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4hwls</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
@@ -1613,17 +1569,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>918</v>
+        <v>167</v>
       </c>
       <c r="Q12" t="n">
-        <v>1807</v>
+        <v>38</v>
       </c>
       <c r="R12" t="n">
-        <v>2725</v>
+        <v>205</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1632,17 +1588,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1394113072</t>
+          <t>2051051265</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1394113072</t>
+          <t>https://m.place.naver.com/place/2051051265</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/종로_PT.xlsx
+++ b/naver-place-crawler/results_health/종로_PT.xlsx
@@ -421,7 +421,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>자마이카피트니스앤스파 종로점</t>
+          <t>백퍼센트짐 헬스&amp;골프</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>jamaica-jongno@naver.com</t>
+          <t>100percentgym2@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1317-8533</t>
+          <t>0507-1345-3897</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 19 르메이에르종로타운1 지하2층~지하3층</t>
+          <t>서울특별시 종로구 대학로 146 B101호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jamaica-jongno</t>
+          <t>https://www.instagram.com/100percent_gym_no.2/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3057</v>
+        <v>1298</v>
       </c>
       <c r="Q3" t="n">
-        <v>503</v>
+        <v>613</v>
       </c>
       <c r="R3" t="n">
-        <v>3560</v>
+        <v>1911</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1716544631</t>
+          <t>1501906296</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1716544631</t>
+          <t>https://m.place.naver.com/place/1501906296</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -747,34 +747,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>스포짐 종각점 PT&amp;헬스</t>
+          <t>어메이징휘트니스 헬스&amp;PT 종로점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>spogym12@naver.com</t>
+          <t>amazinggym_jr@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0507-1351-0020</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 삼봉로 95 대성스카이렉스 B1 스포짐 종각점</t>
+          <t>서울특별시 종로구 수표로 96 10층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spogym12</t>
+          <t>https://blog.naver.com/amazinggym_jr</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -809,13 +805,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>195</v>
+        <v>806</v>
       </c>
       <c r="Q4" t="n">
-        <v>883</v>
+        <v>271</v>
       </c>
       <c r="R4" t="n">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +820,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1991410927</t>
+          <t>1713671108</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1991410927</t>
+          <t>https://m.place.naver.com/place/1713671108</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,39 +842,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>스포짐 종로점 PT&amp;헬스</t>
+          <t>스포짐 종각점 PT&amp;헬스</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>spogym14@naver.com</t>
+          <t>spogym12@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1309-7981</t>
+          <t>0507-1351-0020</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 청계천로 35 관정빌딩 B2 스포짐 종로점</t>
+          <t>서울특별시 종로구 삼봉로 95 대성스카이렉스 B1 스포짐 종각점</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/6/bizes/396022</t>
+          <t>https://blog.naver.com/spogym12</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -903,13 +899,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>235</v>
+        <v>195</v>
       </c>
       <c r="Q5" t="n">
-        <v>712</v>
+        <v>883</v>
       </c>
       <c r="R5" t="n">
-        <v>947</v>
+        <v>1078</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +914,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1240026286</t>
+          <t>1991410927</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1240026286</t>
+          <t>https://m.place.naver.com/place/1991410927</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -940,44 +936,44 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>턴온피트니스 PT 광화문점</t>
+          <t>스포짐 종로점 PT&amp;헬스</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>tndnjsqkek@naver.com</t>
+          <t>spogym14@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1380-6792</t>
+          <t>0507-1309-7981</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로5길 13 2층</t>
+          <t>서울특별시 종로구 청계천로 35 관정빌딩 B2 스포짐 종로점</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/strength_kon</t>
+          <t>https://booking.naver.com/booking/6/bizes/396022</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -997,13 +993,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>34</v>
+        <v>235</v>
       </c>
       <c r="Q6" t="n">
-        <v>212</v>
+        <v>713</v>
       </c>
       <c r="R6" t="n">
-        <v>246</v>
+        <v>948</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,12 +1008,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2018780751</t>
+          <t>1240026286</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2018780751</t>
+          <t>https://m.place.naver.com/place/1240026286</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1029,34 +1025,34 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>스포애니 종각역점</t>
+          <t>턴온피트니스 PT 광화문점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>spoany113@naver.com</t>
+          <t>tndnjsqkek@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1443-9618</t>
+          <t>0507-1380-6792</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 68 B1, B2층</t>
+          <t>서울특별시 종로구 종로5길 13 2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoany113/223842396671</t>
+          <t>https://www.instagram.com/strength_kon</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1071,7 +1067,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1091,13 +1087,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>995</v>
+        <v>34</v>
       </c>
       <c r="Q7" t="n">
-        <v>1660</v>
+        <v>216</v>
       </c>
       <c r="R7" t="n">
-        <v>2655</v>
+        <v>250</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,12 +1102,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1732112209</t>
+          <t>2018780751</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1732112209</t>
+          <t>https://m.place.naver.com/place/2018780751</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1123,34 +1119,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>샤머니짐 헬스&amp;PT 동대문점</t>
+          <t>스포애니 종각역점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>resort_14@naver.com</t>
+          <t>spoany113@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1424-7205</t>
+          <t>0507-1443-9618</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 264 6층</t>
+          <t>서울특별시 종로구 종로 68 B1, B2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/resort_14</t>
+          <t>https://blog.naver.com/spoany113/223842396671</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1185,13 +1181,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>527</v>
+        <v>995</v>
       </c>
       <c r="Q8" t="n">
-        <v>498</v>
+        <v>1660</v>
       </c>
       <c r="R8" t="n">
-        <v>1025</v>
+        <v>2655</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,12 +1196,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1075549287</t>
+          <t>1732112209</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1075549287</t>
+          <t>https://m.place.naver.com/place/1732112209</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1217,34 +1213,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>베럴짐 광화문점</t>
+          <t>샤머니짐 헬스&amp;PT 동대문점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bettergym1@naver.com</t>
+          <t>resort_14@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1353-9536</t>
+          <t>0507-1424-7205</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 새문안로3길 30 대우빌딩 지하1층 123호</t>
+          <t>서울특별시 중구 을지로 264 6층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bettergym1</t>
+          <t>https://blog.naver.com/resort_14</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1279,13 +1275,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>834</v>
+        <v>527</v>
       </c>
       <c r="Q9" t="n">
-        <v>1817</v>
+        <v>498</v>
       </c>
       <c r="R9" t="n">
-        <v>2651</v>
+        <v>1025</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,12 +1290,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1663517273</t>
+          <t>1075549287</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1663517273</t>
+          <t>https://m.place.naver.com/place/1075549287</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1414,33 +1410,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>버핏그라운드 광화문</t>
+          <t>헬스보이짐앤필라걸 서울시청점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>partner@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>healthboy52@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1314-3624</t>
+          <t>0507-1345-4222</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 중구 세종대로 136 B1, B2층</t>
+          <t>서울특별시 중구 무교로 21 지하1층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://pt.butfitground.com/</t>
+          <t>https://www.instagram.com/healthboy52/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1455,7 +1447,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1466,7 +1458,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1475,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>292</v>
+        <v>1017</v>
       </c>
       <c r="Q11" t="n">
-        <v>388</v>
+        <v>1262</v>
       </c>
       <c r="R11" t="n">
-        <v>680</v>
+        <v>2279</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1490,12 +1482,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1720388209</t>
+          <t>1954406967</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1720388209</t>
+          <t>https://m.place.naver.com/place/1954406967</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1512,38 +1504,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>휘트니스피플 우먼 동묘앞역점</t>
+          <t>버핏그라운드 광화문</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>fpeoplew1@naver.com</t>
+          <t>butfitground@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>psi@fitnesspeople.co.kr</t>
+          <t>partner@butfitseoul.com</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1394-3912</t>
+          <t>0507-1314-3624</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 335 7층</t>
+          <t>서울특별시 중구 세종대로 136 B1, B2층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.fitnesspeople.co.kr/</t>
+          <t>https://pt.butfitground.com/</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1564,7 +1556,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1573,13 +1565,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>167</v>
+        <v>292</v>
       </c>
       <c r="Q12" t="n">
-        <v>38</v>
+        <v>388</v>
       </c>
       <c r="R12" t="n">
-        <v>205</v>
+        <v>680</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1588,12 +1580,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2051051265</t>
+          <t>1720388209</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2051051265</t>
+          <t>https://m.place.naver.com/place/1720388209</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">

--- a/naver-place-crawler/results_health/종로_PT.xlsx
+++ b/naver-place-crawler/results_health/종로_PT.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="46" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -586,7 +586,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/acrogym13</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wzdpj6g</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -680,7 +684,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/100percent_gym_no.2/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,7 +694,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -700,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4d9zn</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -718,10 +726,10 @@
         <v>1298</v>
       </c>
       <c r="Q3" t="n">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="R3" t="n">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -747,30 +755,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>어메이징휘트니스 헬스&amp;PT 종로점</t>
+          <t>스포짐 종각점 PT&amp;헬스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>amazinggym_jr@naver.com</t>
+          <t>spogym12@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0507-1351-0020</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 수표로 96 10층</t>
+          <t>서울특별시 종로구 삼봉로 95 대성스카이렉스 B1 스포짐 종각점</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/amazinggym_jr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -780,20 +792,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wchlsb</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -805,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>806</v>
+        <v>195</v>
       </c>
       <c r="Q4" t="n">
-        <v>271</v>
+        <v>883</v>
       </c>
       <c r="R4" t="n">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -820,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1713671108</t>
+          <t>1991410927</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1713671108</t>
+          <t>https://m.place.naver.com/place/1991410927</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -842,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>스포짐 종각점 PT&amp;헬스</t>
+          <t>스포짐 종로점 PT&amp;헬스</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>spogym12@naver.com</t>
+          <t>spogym14@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1351-0020</t>
+          <t>0507-1309-7981</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 삼봉로 95 대성스카이렉스 B1 스포짐 종각점</t>
+          <t>서울특별시 종로구 청계천로 35 관정빌딩 B2 스포짐 종로점</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spogym12</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -874,20 +890,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4ulg5</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -899,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>195</v>
+        <v>235</v>
       </c>
       <c r="Q5" t="n">
-        <v>883</v>
+        <v>714</v>
       </c>
       <c r="R5" t="n">
-        <v>1078</v>
+        <v>949</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -914,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1991410927</t>
+          <t>1240026286</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1991410927</t>
+          <t>https://m.place.naver.com/place/1240026286</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -936,34 +956,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>스포짐 종로점 PT&amp;헬스</t>
+          <t>턴온피트니스 PT 광화문점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>spogym14@naver.com</t>
+          <t>tndnjsqkek@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1309-7981</t>
+          <t>0507-1380-6792</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 청계천로 35 관정빌딩 B2 스포짐 종로점</t>
+          <t>서울특별시 종로구 종로5길 13 2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/6/bizes/396022</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -973,15 +993,19 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/witvn8b</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -993,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>235</v>
+        <v>34</v>
       </c>
       <c r="Q6" t="n">
-        <v>713</v>
+        <v>216</v>
       </c>
       <c r="R6" t="n">
-        <v>948</v>
+        <v>250</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1008,12 +1032,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1240026286</t>
+          <t>2018780751</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1240026286</t>
+          <t>https://m.place.naver.com/place/2018780751</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1025,34 +1049,34 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>턴온피트니스 PT 광화문점</t>
+          <t>스포애니 종각역점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>tndnjsqkek@naver.com</t>
+          <t>spoany113@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1380-6792</t>
+          <t>0507-1443-9618</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로5길 13 2층</t>
+          <t>서울특별시 종로구 종로 68 B1, B2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/strength_kon</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1062,7 +1086,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1072,10 +1096,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w6eii90</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1087,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>34</v>
+        <v>998</v>
       </c>
       <c r="Q7" t="n">
-        <v>216</v>
+        <v>1664</v>
       </c>
       <c r="R7" t="n">
-        <v>250</v>
+        <v>2662</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1102,12 +1130,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2018780751</t>
+          <t>1732112209</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2018780751</t>
+          <t>https://m.place.naver.com/place/1732112209</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1119,34 +1147,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>스포애니 종각역점</t>
+          <t>샤머니짐 헬스&amp;PT 동대문점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>spoany113@naver.com</t>
+          <t>resort_14@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1443-9618</t>
+          <t>0507-1424-7205</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 68 B1, B2층</t>
+          <t>서울특별시 중구 을지로 264 6층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoany113/223842396671</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1156,20 +1184,24 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5vnh2</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1181,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>995</v>
+        <v>527</v>
       </c>
       <c r="Q8" t="n">
-        <v>1660</v>
+        <v>498</v>
       </c>
       <c r="R8" t="n">
-        <v>2655</v>
+        <v>1025</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1196,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1732112209</t>
+          <t>1075549287</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1732112209</t>
+          <t>https://m.place.naver.com/place/1075549287</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1213,34 +1245,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>샤머니짐 헬스&amp;PT 동대문점</t>
+          <t>베럴짐 광화문점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>resort_14@naver.com</t>
+          <t>bettergym1@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1424-7205</t>
+          <t>0507-1353-9536</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 264 6층</t>
+          <t>서울특별시 종로구 새문안로3길 30 대우빌딩 지하1층 123호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/resort_14</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1250,20 +1282,24 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5zxaa</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1275,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>527</v>
+        <v>834</v>
       </c>
       <c r="Q9" t="n">
-        <v>498</v>
+        <v>1818</v>
       </c>
       <c r="R9" t="n">
-        <v>1025</v>
+        <v>2652</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1290,12 +1326,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1075549287</t>
+          <t>1663517273</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1075549287</t>
+          <t>https://m.place.naver.com/place/1663517273</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1358,10 +1394,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4rdsf</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>O</t>
@@ -1376,10 +1416,10 @@
         <v>239</v>
       </c>
       <c r="Q10" t="n">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="R10" t="n">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1405,39 +1445,43 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>헬스보이짐앤필라걸 서울시청점</t>
+          <t>버핏그라운드 PT 광화문</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>healthboy52@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>butfitseoul@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1345-4222</t>
+          <t>0507-1413-0755</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 중구 무교로 21 지하1층</t>
+          <t>서울특별시 중구 세종대로 136 서울파이낸스센터 SFC B1, B2층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/healthboy52/</t>
+          <t>https://www.butfitground.com/4steppt</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1447,7 +1491,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1458,7 +1502,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1467,13 +1511,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1017</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1262</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>2279</v>
+        <v>1</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,12 +1526,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1954406967</t>
+          <t>2093030344</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1954406967</t>
+          <t>https://m.place.naver.com/place/2093030344</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1504,91 +1548,193 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>버핏그라운드 광화문</t>
+          <t>헬스보이짐앤필라걸 서울시청점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>partner@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>healthboy52@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1314-3624</t>
+          <t>0507-1345-4222</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
+          <t>서울특별시 중구 무교로 21 지하1층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4ag5u</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>1018</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1261</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2279</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1954406967</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1954406967</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>버핏그라운드 광화문</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>partner@butfitseoul.com</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1314-3624</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>서울특별시 중구 세종대로 136 B1, B2층</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>https://pt.butfitground.com/</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w6v6jkj</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
         <v>292</v>
       </c>
-      <c r="Q12" t="n">
-        <v>388</v>
-      </c>
-      <c r="R12" t="n">
-        <v>680</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
+      <c r="Q13" t="n">
+        <v>396</v>
+      </c>
+      <c r="R13" t="n">
+        <v>688</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
         <is>
           <t>1720388209</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1720388209</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/종로_PT.xlsx
+++ b/naver-place-crawler/results_health/종로_PT.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="46" customWidth="1" min="7" max="7"/>
-    <col width="38" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -586,7 +586,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/acrogym13</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wzdpj6g</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="Q2" t="n">
         <v>275</v>
       </c>
       <c r="R2" t="n">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,41 +646,41 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>백퍼센트짐 헬스&amp;골프</t>
+          <t>스포짐 종각점 PT&amp;헬스</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>100percentgym2@naver.com</t>
+          <t>spogym12@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1345-3897</t>
+          <t>0507-1351-0020</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 대학로 146 B101호</t>
+          <t>서울특별시 종로구 삼봉로 95 대성스카이렉스 B1 스포짐 종각점</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/spogym12</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,24 +690,20 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4d9zn</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -723,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1298</v>
+        <v>195</v>
       </c>
       <c r="Q3" t="n">
-        <v>614</v>
+        <v>883</v>
       </c>
       <c r="R3" t="n">
-        <v>1912</v>
+        <v>1078</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1501906296</t>
+          <t>1991410927</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1501906296</t>
+          <t>https://m.place.naver.com/place/1991410927</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -760,34 +752,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>스포짐 종각점 PT&amp;헬스</t>
+          <t>스포짐 종로점 PT&amp;헬스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>spogym12@naver.com</t>
+          <t>spogym14@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1351-0020</t>
+          <t>0507-1309-7981</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 삼봉로 95 대성스카이렉스 B1 스포짐 종각점</t>
+          <t>서울특별시 종로구 청계천로 35 관정빌딩 B2 스포짐 종로점</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://booking.naver.com/booking/6/bizes/396022</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -797,19 +789,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wchlsb</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -821,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>195</v>
+        <v>235</v>
       </c>
       <c r="Q4" t="n">
-        <v>883</v>
+        <v>715</v>
       </c>
       <c r="R4" t="n">
-        <v>1078</v>
+        <v>950</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1991410927</t>
+          <t>1240026286</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1991410927</t>
+          <t>https://m.place.naver.com/place/1240026286</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -858,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>스포짐 종로점 PT&amp;헬스</t>
+          <t>턴온피트니스 PT 광화문점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>spogym14@naver.com</t>
+          <t>tndnjsqkek@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1309-7981</t>
+          <t>0507-1380-6792</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 청계천로 35 관정빌딩 B2 스포짐 종로점</t>
+          <t>서울특별시 종로구 종로5길 13 2층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/strength_kon</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -890,7 +878,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -900,14 +888,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4ulg5</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -919,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>235</v>
+        <v>34</v>
       </c>
       <c r="Q5" t="n">
-        <v>714</v>
+        <v>216</v>
       </c>
       <c r="R5" t="n">
-        <v>949</v>
+        <v>250</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,51 +918,51 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1240026286</t>
+          <t>2018780751</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1240026286</t>
+          <t>https://m.place.naver.com/place/2018780751</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>턴온피트니스 PT 광화문점</t>
+          <t>스포애니 종각역점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>tndnjsqkek@naver.com</t>
+          <t>spoany113@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1380-6792</t>
+          <t>0507-1443-9618</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로5길 13 2층</t>
+          <t>서울특별시 종로구 종로 68 B1, B2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/spoany113/223842396671</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -988,24 +972,20 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/witvn8b</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1017,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Q6" t="n">
-        <v>216</v>
+        <v>1664</v>
       </c>
       <c r="R6" t="n">
-        <v>250</v>
+        <v>2664</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,51 +1012,51 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2018780751</t>
+          <t>1732112209</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2018780751</t>
+          <t>https://m.place.naver.com/place/1732112209</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>스포애니 종각역점</t>
+          <t>샤머니짐 헬스&amp;PT 동대문점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>spoany113@naver.com</t>
+          <t>resort_14@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1443-9618</t>
+          <t>0507-1424-7205</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 68 B1, B2층</t>
+          <t>서울특별시 중구 을지로 264 6층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/resort_14</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1086,24 +1066,20 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w6eii90</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1115,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>998</v>
+        <v>528</v>
       </c>
       <c r="Q7" t="n">
-        <v>1664</v>
+        <v>499</v>
       </c>
       <c r="R7" t="n">
-        <v>2662</v>
+        <v>1027</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,51 +1106,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1732112209</t>
+          <t>1075549287</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1732112209</t>
+          <t>https://m.place.naver.com/place/1075549287</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>샤머니짐 헬스&amp;PT 동대문점</t>
+          <t>스포애니 서울시청역점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>resort_14@naver.com</t>
+          <t>spoany_73@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1424-7205</t>
+          <t>0507-1335-5273</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 264 6층</t>
+          <t>서울특별시 중구 서소문로 124 씨티스퀘어 B2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/spoany_73</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1184,24 +1160,20 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5vnh2</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1209,17 +1181,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>527</v>
+        <v>920</v>
       </c>
       <c r="Q8" t="n">
-        <v>498</v>
+        <v>1812</v>
       </c>
       <c r="R8" t="n">
-        <v>1025</v>
+        <v>2732</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,17 +1200,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1075549287</t>
+          <t>1394113072</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1075549287</t>
+          <t>https://m.place.naver.com/place/1394113072</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1250,29 +1222,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>베럴짐 광화문점</t>
+          <t>런광화문</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bettergym1@naver.com</t>
+          <t>projectfithouse@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1353-9536</t>
+          <t>0507-1331-5403</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 새문안로3길 30 대우빌딩 지하1층 123호</t>
+          <t>서울특별시 종로구 새문안로3길 30 지하1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.projectrun.co.kr</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1282,24 +1254,20 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5zxaa</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1311,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>834</v>
+        <v>474</v>
       </c>
       <c r="Q9" t="n">
-        <v>1818</v>
+        <v>347</v>
       </c>
       <c r="R9" t="n">
-        <v>2652</v>
+        <v>821</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,60 +1294,56 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1663517273</t>
+          <t>1763606096</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1663517273</t>
+          <t>https://m.place.naver.com/place/1763606096</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>마이크로스튜디오 시청점</t>
+          <t>스포애니 광화문역점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>cityhallmicro@naver.com</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>owner@microstudio.kr</t>
-        </is>
-      </c>
+          <t>spoany56@naver.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1346-2162</t>
+          <t>0507-1398-9618</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 중구 다동길 43 한외빌딩 지하1층 마이크로스튜디오</t>
+          <t>서울특별시 종로구 새문안로 82 에스타워</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://microstudio.kr</t>
+          <t>https://blog.naver.com/spoany56</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1394,17 +1358,13 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4rdsf</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1413,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>239</v>
+        <v>908</v>
       </c>
       <c r="Q10" t="n">
-        <v>745</v>
+        <v>2325</v>
       </c>
       <c r="R10" t="n">
-        <v>984</v>
+        <v>3233</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1428,60 +1388,56 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1381838006</t>
+          <t>1632291613</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1381838006</t>
+          <t>https://m.place.naver.com/place/1632291613</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>버핏그라운드 PT 광화문</t>
+          <t>짐구공 헬스 PT 골프 광화문점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>butfitseoul@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>sujjong1015@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1413-0755</t>
+          <t>0507-1389-0825</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 중구 세종대로 136 서울파이낸스센터 SFC B1, B2층</t>
+          <t>서울특별시 중구 무교로 16 9층, 10층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.butfitground.com/4steppt</t>
+          <t>https://buly.kr/613HU8T</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1502,7 +1458,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1511,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>723</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>1225</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1526,217 +1482,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2093030344</t>
+          <t>1816876645</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2093030344</t>
+          <t>https://m.place.naver.com/place/1816876645</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>헬스보이짐앤필라걸 서울시청점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>healthboy52@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1345-4222</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>서울특별시 중구 무교로 21 지하1층</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4ag5u</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>1018</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1261</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2279</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1954406967</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1954406967</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>버핏그라운드 광화문</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>partner@butfitseoul.com</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1314-3624</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>서울특별시 중구 세종대로 136 B1, B2층</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://pt.butfitground.com/</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w6v6jkj</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>292</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>396</v>
-      </c>
-      <c r="R13" t="n">
-        <v>688</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1720388209</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1720388209</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/종로_PT.xlsx
+++ b/naver-place-crawler/results_health/종로_PT.xlsx
@@ -421,12 +421,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>아크로짐 안국역점 헬스&amp;PT</t>
+          <t>백퍼센트짐 헬스&amp;골프</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>acrogym7487@naver.com</t>
+          <t>100percentgym2@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1448-0665</t>
+          <t>0507-1345-3897</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 삼일대로 469 서원빌딩 지하2층 아크로짐 안국역점 헬스앤PT</t>
+          <t>서울특별시 종로구 대학로 146 B101호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/acrogym13</t>
+          <t>https://www.instagram.com/100percent_gym_no.2/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>618</v>
+        <v>1298</v>
       </c>
       <c r="Q2" t="n">
-        <v>275</v>
+        <v>616</v>
       </c>
       <c r="R2" t="n">
-        <v>893</v>
+        <v>1914</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>17919627</t>
+          <t>1501906296</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/17919627</t>
+          <t>https://m.place.naver.com/place/1501906296</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -653,34 +653,30 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>스포짐 종각점 PT&amp;헬스</t>
+          <t>어메이징휘트니스 헬스&amp;PT 종로점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>spogym12@naver.com</t>
+          <t>amazinggym_jr@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0507-1351-0020</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 삼봉로 95 대성스카이렉스 B1 스포짐 종각점</t>
+          <t>서울특별시 종로구 수표로 96 10층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spogym12</t>
+          <t>https://blog.naver.com/amazinggym_jr</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -715,13 +711,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>195</v>
+        <v>806</v>
       </c>
       <c r="Q3" t="n">
-        <v>883</v>
+        <v>271</v>
       </c>
       <c r="R3" t="n">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +726,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1991410927</t>
+          <t>1713671108</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1991410927</t>
+          <t>https://m.place.naver.com/place/1713671108</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -747,44 +743,44 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>스포짐 종로점 PT&amp;헬스</t>
+          <t>자마이카피트니스앤스파 종로점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>spogym14@naver.com</t>
+          <t>jamaica-jongno@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1309-7981</t>
+          <t>0507-1317-8533</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 청계천로 35 관정빌딩 B2 스포짐 종로점</t>
+          <t>서울특별시 종로구 종로 19 르메이에르종로타운1 지하2층~지하3층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/6/bizes/396022</t>
+          <t>https://blog.naver.com/jamaica-jongno</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -809,13 +805,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>235</v>
+        <v>3066</v>
       </c>
       <c r="Q4" t="n">
-        <v>715</v>
+        <v>504</v>
       </c>
       <c r="R4" t="n">
-        <v>950</v>
+        <v>3570</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +820,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1240026286</t>
+          <t>1716544631</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1240026286</t>
+          <t>https://m.place.naver.com/place/1716544631</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,29 +842,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>턴온피트니스 PT 광화문점</t>
+          <t>스포짐 종각점 PT&amp;헬스</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>tndnjsqkek@naver.com</t>
+          <t>spogym12@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1380-6792</t>
+          <t>0507-1351-0020</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로5길 13 2층</t>
+          <t>서울특별시 종로구 삼봉로 95 대성스카이렉스 B1 스포짐 종각점</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/strength_kon</t>
+          <t>https://blog.naver.com/spogym12</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -883,7 +879,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -903,13 +899,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="Q5" t="n">
-        <v>216</v>
+        <v>885</v>
       </c>
       <c r="R5" t="n">
-        <v>250</v>
+        <v>1080</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +914,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2018780751</t>
+          <t>1991410927</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2018780751</t>
+          <t>https://m.place.naver.com/place/1991410927</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -935,44 +931,44 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>스포애니 종각역점</t>
+          <t>스포짐 종로점 PT&amp;헬스</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>spoany113@naver.com</t>
+          <t>spogym14@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1443-9618</t>
+          <t>0507-1309-7981</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 68 B1, B2층</t>
+          <t>서울특별시 종로구 청계천로 35 관정빌딩 B2 스포짐 종로점</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoany113/223842396671</t>
+          <t>https://booking.naver.com/booking/6/bizes/396022</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -997,13 +993,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1000</v>
+        <v>235</v>
       </c>
       <c r="Q6" t="n">
-        <v>1664</v>
+        <v>720</v>
       </c>
       <c r="R6" t="n">
-        <v>2664</v>
+        <v>955</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,12 +1008,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1732112209</t>
+          <t>1240026286</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1732112209</t>
+          <t>https://m.place.naver.com/place/1240026286</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1029,34 +1025,34 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>샤머니짐 헬스&amp;PT 동대문점</t>
+          <t>스포애니 종각역점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>resort_14@naver.com</t>
+          <t>spoany113@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1424-7205</t>
+          <t>0507-1443-9618</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 264 6층</t>
+          <t>서울특별시 종로구 종로 68 B1, B2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/resort_14</t>
+          <t>https://blog.naver.com/spoany113/223842396671</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,13 +1087,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>528</v>
+        <v>1000</v>
       </c>
       <c r="Q7" t="n">
-        <v>499</v>
+        <v>1664</v>
       </c>
       <c r="R7" t="n">
-        <v>1027</v>
+        <v>2664</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,12 +1102,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1075549287</t>
+          <t>1732112209</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1075549287</t>
+          <t>https://m.place.naver.com/place/1732112209</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1123,34 +1119,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>스포애니 서울시청역점</t>
+          <t>샤머니짐 헬스&amp;PT 동대문점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>spoany_73@naver.com</t>
+          <t>resort_14@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1335-5273</t>
+          <t>0507-1424-7205</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 중구 서소문로 124 씨티스퀘어 B2층</t>
+          <t>서울특별시 중구 을지로 264 6층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoany_73</t>
+          <t>https://blog.naver.com/resort_14</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1181,17 +1177,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>920</v>
+        <v>528</v>
       </c>
       <c r="Q8" t="n">
-        <v>1812</v>
+        <v>500</v>
       </c>
       <c r="R8" t="n">
-        <v>2732</v>
+        <v>1028</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,12 +1196,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1394113072</t>
+          <t>1075549287</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1394113072</t>
+          <t>https://m.place.naver.com/place/1075549287</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1217,34 +1213,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>런광화문</t>
+          <t>턴온피트니스 PT 광화문점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>projectfithouse@naver.com</t>
+          <t>tndnjsqkek@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1331-5403</t>
+          <t>0507-1380-6792</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 새문안로3길 30 지하1층</t>
+          <t>서울특별시 종로구 종로5길 13 2층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.projectrun.co.kr</t>
+          <t>https://www.instagram.com/strength_kon</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1259,7 +1255,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1279,13 +1275,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>474</v>
+        <v>34</v>
       </c>
       <c r="Q9" t="n">
-        <v>347</v>
+        <v>217</v>
       </c>
       <c r="R9" t="n">
-        <v>821</v>
+        <v>251</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,12 +1290,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1763606096</t>
+          <t>2018780751</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1763606096</t>
+          <t>https://m.place.naver.com/place/2018780751</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1316,29 +1312,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>스포애니 광화문역점</t>
+          <t>베럴짐 광화문점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>spoany56@naver.com</t>
+          <t>bettergym1@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1398-9618</t>
+          <t>0507-1353-9536</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 새문안로 82 에스타워</t>
+          <t>서울특별시 종로구 새문안로3길 30 대우빌딩 지하1층 123호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoany56</t>
+          <t>https://blog.naver.com/bettergym1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1373,13 +1369,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>908</v>
+        <v>834</v>
       </c>
       <c r="Q10" t="n">
-        <v>2325</v>
+        <v>1808</v>
       </c>
       <c r="R10" t="n">
-        <v>3233</v>
+        <v>2642</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,12 +1384,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1632291613</t>
+          <t>1663517273</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1632291613</t>
+          <t>https://m.place.naver.com/place/1663517273</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1410,29 +1406,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>짐구공 헬스 PT 골프 광화문점</t>
+          <t>헬스보이짐앤필라걸 서울시청점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>sujjong1015@naver.com</t>
+          <t>healthboy52@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1389-0825</t>
+          <t>0507-1345-4222</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 중구 무교로 16 9층, 10층</t>
+          <t>서울특별시 중구 무교로 21 지하1층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://buly.kr/613HU8T</t>
+          <t>https://www.instagram.com/healthboy52/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1447,7 +1443,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1467,13 +1463,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>502</v>
+        <v>1019</v>
       </c>
       <c r="Q11" t="n">
-        <v>723</v>
+        <v>1262</v>
       </c>
       <c r="R11" t="n">
-        <v>1225</v>
+        <v>2281</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,12 +1478,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1816876645</t>
+          <t>1954406967</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1816876645</t>
+          <t>https://m.place.naver.com/place/1954406967</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/종로_PT.xlsx
+++ b/naver-place-crawler/results_health/종로_PT.xlsx
@@ -422,11 +422,11 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>백퍼센트짐 헬스&amp;골프</t>
+          <t>아크로짐 안국역점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>100percentgym2@naver.com</t>
+          <t>acrogym7487@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1345-3897</t>
+          <t>0507-1448-0665</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 대학로 146 B101호</t>
+          <t>서울특별시 종로구 삼일대로 469 서원빌딩 지하2층 아크로짐 안국역점 헬스앤PT</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/100percent_gym_no.2/</t>
+          <t>https://www.instagram.com/acrogym13</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1298</v>
+        <v>618</v>
       </c>
       <c r="Q2" t="n">
-        <v>616</v>
+        <v>276</v>
       </c>
       <c r="R2" t="n">
-        <v>1914</v>
+        <v>894</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1501906296</t>
+          <t>17919627</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1501906296</t>
+          <t>https://m.place.naver.com/place/17919627</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -711,13 +711,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="Q3" t="n">
         <v>271</v>
       </c>
       <c r="R3" t="n">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -736,41 +736,41 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>자마이카피트니스앤스파 종로점</t>
+          <t>스포짐 종각점 PT&amp;헬스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>jamaica-jongno@naver.com</t>
+          <t>spogym12@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1317-8533</t>
+          <t>0507-1351-0020</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 19 르메이에르종로타운1 지하2층~지하3층</t>
+          <t>서울특별시 종로구 삼봉로 95 대성스카이렉스 B1 스포짐 종각점</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jamaica-jongno</t>
+          <t>https://blog.naver.com/spogym12</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -805,13 +805,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3066</v>
+        <v>195</v>
       </c>
       <c r="Q4" t="n">
-        <v>504</v>
+        <v>885</v>
       </c>
       <c r="R4" t="n">
-        <v>3570</v>
+        <v>1080</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -820,17 +820,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1716544631</t>
+          <t>1991410927</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1716544631</t>
+          <t>https://m.place.naver.com/place/1991410927</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -842,39 +842,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>스포짐 종각점 PT&amp;헬스</t>
+          <t>스포짐 종로점 PT&amp;헬스</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>spogym12@naver.com</t>
+          <t>spogym14@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1351-0020</t>
+          <t>0507-1309-7981</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 삼봉로 95 대성스카이렉스 B1 스포짐 종각점</t>
+          <t>서울특별시 종로구 청계천로 35 관정빌딩 B2 스포짐 종로점</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spogym12</t>
+          <t>https://booking.naver.com/booking/6/bizes/396022</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -899,13 +899,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>195</v>
+        <v>235</v>
       </c>
       <c r="Q5" t="n">
-        <v>885</v>
+        <v>721</v>
       </c>
       <c r="R5" t="n">
-        <v>1080</v>
+        <v>956</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -914,61 +914,61 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1991410927</t>
+          <t>1240026286</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1991410927</t>
+          <t>https://m.place.naver.com/place/1240026286</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>스포짐 종로점 PT&amp;헬스</t>
+          <t>스포애니 종각역점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>spogym14@naver.com</t>
+          <t>spoany113@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1309-7981</t>
+          <t>0507-1443-9618</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 청계천로 35 관정빌딩 B2 스포짐 종로점</t>
+          <t>서울특별시 종로구 종로 68 B1, B2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/6/bizes/396022</t>
+          <t>https://blog.naver.com/spoany113/223842396671</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>235</v>
+        <v>1000</v>
       </c>
       <c r="Q6" t="n">
-        <v>720</v>
+        <v>1664</v>
       </c>
       <c r="R6" t="n">
-        <v>955</v>
+        <v>2664</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1008,51 +1008,51 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1240026286</t>
+          <t>1732112209</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1240026286</t>
+          <t>https://m.place.naver.com/place/1732112209</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>스포애니 종각역점</t>
+          <t>샤머니짐 헬스&amp;PT 동대문점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>spoany113@naver.com</t>
+          <t>resort_14@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1443-9618</t>
+          <t>0507-1424-7205</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 68 B1, B2층</t>
+          <t>서울특별시 중구 을지로 264 6층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoany113/223842396671</t>
+          <t>https://blog.naver.com/resort_14</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1000</v>
+        <v>530</v>
       </c>
       <c r="Q7" t="n">
-        <v>1664</v>
+        <v>500</v>
       </c>
       <c r="R7" t="n">
-        <v>2664</v>
+        <v>1030</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1732112209</t>
+          <t>1075549287</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1732112209</t>
+          <t>https://m.place.naver.com/place/1075549287</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1124,29 +1124,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>샤머니짐 헬스&amp;PT 동대문점</t>
+          <t>턴온피트니스 PT 광화문점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>resort_14@naver.com</t>
+          <t>tndnjsqkek@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1424-7205</t>
+          <t>0507-1380-6792</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 264 6층</t>
+          <t>서울특별시 종로구 종로5길 13 2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/resort_14</t>
+          <t>https://www.instagram.com/strength_kon</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1181,13 +1181,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>528</v>
+        <v>34</v>
       </c>
       <c r="Q8" t="n">
-        <v>500</v>
+        <v>217</v>
       </c>
       <c r="R8" t="n">
-        <v>1028</v>
+        <v>251</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1196,17 +1196,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1075549287</t>
+          <t>2018780751</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1075549287</t>
+          <t>https://m.place.naver.com/place/2018780751</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1218,34 +1218,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>턴온피트니스 PT 광화문점</t>
+          <t>마이크로스튜디오 시청점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>tndnjsqkek@naver.com</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>cityhallmicro@naver.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>owner@microstudio.kr</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1380-6792</t>
+          <t>0507-1346-2162</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로5길 13 2층</t>
+          <t>서울특별시 중구 다동길 43 한외빌딩 지하1층 마이크로스튜디오</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/strength_kon</t>
+          <t>https://microstudio.kr</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1255,7 +1259,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1266,7 +1270,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1275,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>34</v>
+        <v>239</v>
       </c>
       <c r="Q9" t="n">
-        <v>217</v>
+        <v>746</v>
       </c>
       <c r="R9" t="n">
-        <v>251</v>
+        <v>985</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1290,17 +1294,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2018780751</t>
+          <t>1381838006</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2018780751</t>
+          <t>https://m.place.naver.com/place/1381838006</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1312,34 +1316,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>베럴짐 광화문점</t>
+          <t>팀버핏 광화문</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bettergym1@naver.com</t>
+          <t>jhjh5508@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0507-1353-9536</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 새문안로3길 30 대우빌딩 지하1층 123호</t>
+          <t>서울특별시 중구 세종대로 136 지하 1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bettergym1</t>
+          <t>https://www.teambutfit.com</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1369,13 +1369,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>834</v>
+        <v>240</v>
       </c>
       <c r="Q10" t="n">
-        <v>1808</v>
+        <v>34</v>
       </c>
       <c r="R10" t="n">
-        <v>2642</v>
+        <v>274</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1384,56 +1384,60 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1663517273</t>
+          <t>1117727301</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1663517273</t>
+          <t>https://m.place.naver.com/place/1117727301</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>헬스보이짐앤필라걸 서울시청점</t>
+          <t>버핏그라운드 PT 광화문</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>healthboy52@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>butfitseoul@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1345-4222</t>
+          <t>0507-1413-0755</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 중구 무교로 21 지하1층</t>
+          <t>서울특별시 중구 세종대로 136 서울파이낸스센터 SFC B1, B2층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/healthboy52/</t>
+          <t>https://www.butfitground.com/4steppt</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1443,7 +1447,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1454,7 +1458,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1463,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1019</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1262</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>2281</v>
+        <v>1</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1478,17 +1482,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1954406967</t>
+          <t>2093030344</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1954406967</t>
+          <t>https://m.place.naver.com/place/2093030344</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/종로_PT.xlsx
+++ b/naver-place-crawler/results_health/종로_PT.xlsx
@@ -423,7 +423,7 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="46" customWidth="1" min="7" max="7"/>
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,29 +564,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>아크로짐 안국역점 헬스&amp;PT</t>
+          <t>어메이징휘트니스 헬스&amp;PT 종로점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>acrogym7487@naver.com</t>
+          <t>amazinggym_jr@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0507-1448-0665</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 삼일대로 469 서원빌딩 지하2층 아크로짐 안국역점 헬스앤PT</t>
+          <t>서울특별시 종로구 수표로 96 10층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/acrogym13</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,7 +592,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -606,10 +602,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/ww2tdzj</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>618</v>
+        <v>808</v>
       </c>
       <c r="Q2" t="n">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="R2" t="n">
-        <v>894</v>
+        <v>1079</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>17919627</t>
+          <t>1713671108</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/17919627</t>
+          <t>https://m.place.naver.com/place/1713671108</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -653,30 +653,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>어메이징휘트니스 헬스&amp;PT 종로점</t>
+          <t>스포짐 종각점 PT&amp;헬스</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>amazinggym_jr@naver.com</t>
+          <t>spogym12@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0507-1351-0020</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 수표로 96 10층</t>
+          <t>서울특별시 종로구 삼봉로 95 대성스카이렉스 B1 스포짐 종각점</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/amazinggym_jr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -686,20 +690,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wchlsb</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -711,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>808</v>
+        <v>195</v>
       </c>
       <c r="Q3" t="n">
-        <v>271</v>
+        <v>885</v>
       </c>
       <c r="R3" t="n">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -726,12 +734,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1713671108</t>
+          <t>1991410927</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1713671108</t>
+          <t>https://m.place.naver.com/place/1991410927</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -748,39 +756,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>스포짐 종각점 PT&amp;헬스</t>
+          <t>스포짐 종로점 PT&amp;헬스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>spogym12@naver.com</t>
+          <t>spogym14@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1351-0020</t>
+          <t>0507-1309-7981</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 삼봉로 95 대성스카이렉스 B1 스포짐 종각점</t>
+          <t>서울특별시 종로구 청계천로 35 관정빌딩 B2 스포짐 종로점</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spogym12</t>
+          <t>https://booking.naver.com/booking/6/bizes/396022</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -805,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>195</v>
+        <v>235</v>
       </c>
       <c r="Q4" t="n">
-        <v>885</v>
+        <v>724</v>
       </c>
       <c r="R4" t="n">
-        <v>1080</v>
+        <v>959</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -820,12 +828,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1991410927</t>
+          <t>1240026286</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1991410927</t>
+          <t>https://m.place.naver.com/place/1240026286</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -837,39 +845,39 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>스포짐 종로점 PT&amp;헬스</t>
+          <t>스포애니 종각역점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>spogym14@naver.com</t>
+          <t>spoany113@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1309-7981</t>
+          <t>0507-1443-9618</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 청계천로 35 관정빌딩 B2 스포짐 종로점</t>
+          <t>서울특별시 종로구 종로 68 B1, B2층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/6/bizes/396022</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -879,15 +887,19 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w6eii90</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -899,13 +911,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>235</v>
+        <v>1000</v>
       </c>
       <c r="Q5" t="n">
-        <v>721</v>
+        <v>1664</v>
       </c>
       <c r="R5" t="n">
-        <v>956</v>
+        <v>2664</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -914,12 +926,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1240026286</t>
+          <t>1732112209</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1240026286</t>
+          <t>https://m.place.naver.com/place/1732112209</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -931,34 +943,34 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>스포애니 종각역점</t>
+          <t>샤머니짐 헬스&amp;PT 동대문점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>spoany113@naver.com</t>
+          <t>resort_14@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1443-9618</t>
+          <t>0507-1424-7205</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 68 B1, B2층</t>
+          <t>서울특별시 중구 을지로 264 6층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoany113/223842396671</t>
+          <t>https://blog.naver.com/resort_14</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -993,13 +1005,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1000</v>
+        <v>530</v>
       </c>
       <c r="Q6" t="n">
-        <v>1664</v>
+        <v>500</v>
       </c>
       <c r="R6" t="n">
-        <v>2664</v>
+        <v>1030</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1008,12 +1020,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1732112209</t>
+          <t>1075549287</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1732112209</t>
+          <t>https://m.place.naver.com/place/1075549287</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1030,29 +1042,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>샤머니짐 헬스&amp;PT 동대문점</t>
+          <t>턴온피트니스 PT 광화문점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>resort_14@naver.com</t>
+          <t>tndnjsqkek@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1424-7205</t>
+          <t>0507-1380-6792</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 264 6층</t>
+          <t>서울특별시 종로구 종로5길 13 2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/resort_14</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1062,20 +1074,24 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/witvn8b</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1087,13 +1103,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>530</v>
+        <v>34</v>
       </c>
       <c r="Q7" t="n">
-        <v>500</v>
+        <v>222</v>
       </c>
       <c r="R7" t="n">
-        <v>1030</v>
+        <v>256</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1102,12 +1118,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1075549287</t>
+          <t>2018780751</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1075549287</t>
+          <t>https://m.place.naver.com/place/2018780751</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1124,34 +1140,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>턴온피트니스 PT 광화문점</t>
+          <t>마이크로스튜디오 시청점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>tndnjsqkek@naver.com</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>cityhallmicro@naver.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>owner@microstudio.kr</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1380-6792</t>
+          <t>0507-1346-2162</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로5길 13 2층</t>
+          <t>서울특별시 중구 다동길 43 한외빌딩 지하1층 마이크로스튜디오</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/strength_kon</t>
+          <t>https://microstudio.kr</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1161,18 +1181,22 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4rdsf</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1181,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>34</v>
+        <v>239</v>
       </c>
       <c r="Q8" t="n">
-        <v>217</v>
+        <v>746</v>
       </c>
       <c r="R8" t="n">
-        <v>251</v>
+        <v>985</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1196,12 +1220,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2018780751</t>
+          <t>1381838006</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2018780751</t>
+          <t>https://m.place.naver.com/place/1381838006</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1213,64 +1237,64 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>마이크로스튜디오 시청점</t>
+          <t>아크로짐 안국역점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>cityhallmicro@naver.com</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>owner@microstudio.kr</t>
-        </is>
-      </c>
+          <t>acrogym7487@naver.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1346-2162</t>
+          <t>0507-1448-0665</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 중구 다동길 43 한외빌딩 지하1층 마이크로스튜디오</t>
+          <t>서울특별시 종로구 삼일대로 469 서원빌딩 지하2층 아크로짐 안국역점 헬스앤PT</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://microstudio.kr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wzdpj6g</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1279,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>239</v>
+        <v>618</v>
       </c>
       <c r="Q9" t="n">
-        <v>746</v>
+        <v>276</v>
       </c>
       <c r="R9" t="n">
-        <v>985</v>
+        <v>894</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,12 +1318,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1381838006</t>
+          <t>17919627</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1381838006</t>
+          <t>https://m.place.naver.com/place/17919627</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1316,35 +1340,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>팀버핏 광화문</t>
+          <t>헬스보이짐앤필라걸 서울시청점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>jhjh5508@naver.com</t>
+          <t>healthboy52@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0507-1345-4222</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 중구 세종대로 136 지하 1층</t>
+          <t>서울특별시 중구 무교로 21 지하1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.teambutfit.com</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1354,10 +1382,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4ag5u</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1369,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>240</v>
+        <v>1019</v>
       </c>
       <c r="Q10" t="n">
-        <v>34</v>
+        <v>1265</v>
       </c>
       <c r="R10" t="n">
-        <v>274</v>
+        <v>2284</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1384,12 +1416,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1117727301</t>
+          <t>1954406967</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1117727301</t>
+          <t>https://m.place.naver.com/place/1954406967</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1401,38 +1433,38 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>버핏그라운드 PT 광화문</t>
+          <t>휘트니스피플 우먼 동묘앞역점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
+          <t>fpeoplew1@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>butfitseoul@butfitseoul.com</t>
+          <t>psi@fitnesspeople.co.kr</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1413-0755</t>
+          <t>0507-1394-3912</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 중구 세종대로 136 서울파이낸스센터 SFC B1, B2층</t>
+          <t>서울특별시 종로구 종로 335 7층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.butfitground.com/4steppt</t>
+          <t>https://www.fitnesspeople.co.kr/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1452,13 +1484,17 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w3icahd</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1467,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>215</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,12 +1518,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2093030344</t>
+          <t>2051051265</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2093030344</t>
+          <t>https://m.place.naver.com/place/2051051265</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
